--- a/SALT/data_for_ternary_script.xlsx
+++ b/SALT/data_for_ternary_script.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/spreadsheets/SALT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A513F1B-87E4-3246-A22E-39F99E4906F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB32512B-CC39-B34D-AEB9-FD420CF01408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9860" yWindow="3500" windowWidth="27240" windowHeight="16440" xr2:uid="{D1E83D82-F35D-5845-B7E9-3C059027DF94}"/>
+    <workbookView xWindow="9780" yWindow="500" windowWidth="19020" windowHeight="16020" xr2:uid="{D1E83D82-F35D-5845-B7E9-3C059027DF94}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="density" sheetId="1" r:id="rId1"/>
+    <sheet name="cp" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
   <si>
     <t>LiCl</t>
   </si>
@@ -66,6 +67,21 @@
   </si>
   <si>
     <t>1.287242651])</t>
+  </si>
+  <si>
+    <t>np.array([1</t>
+  </si>
+  <si>
+    <t>0.33375])</t>
+  </si>
+  <si>
+    <t>np.array([0</t>
+  </si>
+  <si>
+    <t>NaCl</t>
+  </si>
+  <si>
+    <t>0.3325])</t>
   </si>
 </sst>
 </file>
@@ -437,10 +453,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F60CAD4-C494-BD49-A9A9-E7F2CB2D7D97}">
-  <dimension ref="A4:X8"/>
+  <dimension ref="A4:AX55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -514,7 +530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -588,7 +604,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:48" x14ac:dyDescent="0.2">
       <c r="D6">
         <f>1-D4-D5</f>
         <v>0.2</v>
@@ -670,7 +686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -718,6 +734,2931 @@
       </c>
       <c r="P8" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>1.391679723207335</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0.9</v>
+      </c>
+      <c r="J13">
+        <v>0.8</v>
+      </c>
+      <c r="K13">
+        <v>0.7</v>
+      </c>
+      <c r="L13">
+        <v>0.6</v>
+      </c>
+      <c r="M13">
+        <v>0.5</v>
+      </c>
+      <c r="N13">
+        <v>0.4</v>
+      </c>
+      <c r="O13">
+        <v>0.3</v>
+      </c>
+      <c r="P13">
+        <v>0.2</v>
+      </c>
+      <c r="Q13">
+        <v>0.1</v>
+      </c>
+      <c r="R13">
+        <v>0.9</v>
+      </c>
+      <c r="S13">
+        <v>0.8</v>
+      </c>
+      <c r="T13">
+        <v>0.7</v>
+      </c>
+      <c r="U13">
+        <v>0.6</v>
+      </c>
+      <c r="V13">
+        <v>0.5</v>
+      </c>
+      <c r="W13">
+        <v>0.4</v>
+      </c>
+      <c r="X13">
+        <v>0.3</v>
+      </c>
+      <c r="Y13">
+        <v>0.2</v>
+      </c>
+      <c r="Z13">
+        <v>0.1</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0.8</v>
+      </c>
+      <c r="AK13">
+        <v>0.6</v>
+      </c>
+      <c r="AL13">
+        <v>0.4</v>
+      </c>
+      <c r="AM13">
+        <v>0.2</v>
+      </c>
+      <c r="AN13">
+        <v>0.1</v>
+      </c>
+      <c r="AO13">
+        <v>0.2</v>
+      </c>
+      <c r="AP13">
+        <v>0.3</v>
+      </c>
+      <c r="AQ13">
+        <v>0.4</v>
+      </c>
+      <c r="AR13">
+        <v>0.1</v>
+      </c>
+      <c r="AS13">
+        <v>0.2</v>
+      </c>
+      <c r="AT13">
+        <v>0.3</v>
+      </c>
+      <c r="AU13">
+        <v>0.4</v>
+      </c>
+      <c r="AV13">
+        <v>0.33374999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>1.3481419848321696</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0.1</v>
+      </c>
+      <c r="J14">
+        <v>0.2</v>
+      </c>
+      <c r="K14">
+        <v>0.3</v>
+      </c>
+      <c r="L14">
+        <v>0.4</v>
+      </c>
+      <c r="M14">
+        <v>0.5</v>
+      </c>
+      <c r="N14">
+        <v>0.6</v>
+      </c>
+      <c r="O14">
+        <v>0.7</v>
+      </c>
+      <c r="P14">
+        <v>0.8</v>
+      </c>
+      <c r="Q14">
+        <v>0.9</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0.9</v>
+      </c>
+      <c r="AB14">
+        <v>0.8</v>
+      </c>
+      <c r="AC14">
+        <v>0.7</v>
+      </c>
+      <c r="AD14">
+        <v>0.6</v>
+      </c>
+      <c r="AE14">
+        <v>0.5</v>
+      </c>
+      <c r="AF14">
+        <v>0.4</v>
+      </c>
+      <c r="AG14">
+        <v>0.3</v>
+      </c>
+      <c r="AH14">
+        <v>0.2</v>
+      </c>
+      <c r="AI14">
+        <v>0.1</v>
+      </c>
+      <c r="AJ14">
+        <v>0.1</v>
+      </c>
+      <c r="AK14">
+        <v>0.2</v>
+      </c>
+      <c r="AL14">
+        <v>0.3</v>
+      </c>
+      <c r="AM14">
+        <v>0.4</v>
+      </c>
+      <c r="AN14">
+        <v>0.8</v>
+      </c>
+      <c r="AO14">
+        <v>0.6</v>
+      </c>
+      <c r="AP14">
+        <v>0.4</v>
+      </c>
+      <c r="AQ14">
+        <v>0.2</v>
+      </c>
+      <c r="AR14">
+        <v>0.1</v>
+      </c>
+      <c r="AS14">
+        <v>0.2</v>
+      </c>
+      <c r="AT14">
+        <v>0.3</v>
+      </c>
+      <c r="AU14">
+        <v>0.4</v>
+      </c>
+      <c r="AV14">
+        <v>0.33374999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1.4564030781352593</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0.1</v>
+      </c>
+      <c r="S15">
+        <v>0.2</v>
+      </c>
+      <c r="T15">
+        <v>0.3</v>
+      </c>
+      <c r="U15">
+        <v>0.4</v>
+      </c>
+      <c r="V15">
+        <v>0.5</v>
+      </c>
+      <c r="W15">
+        <v>0.6</v>
+      </c>
+      <c r="X15">
+        <v>0.7</v>
+      </c>
+      <c r="Y15">
+        <v>0.8</v>
+      </c>
+      <c r="Z15">
+        <v>0.9</v>
+      </c>
+      <c r="AA15">
+        <v>0.1</v>
+      </c>
+      <c r="AB15">
+        <v>0.2</v>
+      </c>
+      <c r="AC15">
+        <v>0.3</v>
+      </c>
+      <c r="AD15">
+        <v>0.4</v>
+      </c>
+      <c r="AE15">
+        <v>0.5</v>
+      </c>
+      <c r="AF15">
+        <v>0.6</v>
+      </c>
+      <c r="AG15">
+        <v>0.7</v>
+      </c>
+      <c r="AH15">
+        <v>0.8</v>
+      </c>
+      <c r="AI15">
+        <v>0.9</v>
+      </c>
+      <c r="AJ15">
+        <v>0.1</v>
+      </c>
+      <c r="AK15">
+        <v>0.2</v>
+      </c>
+      <c r="AL15">
+        <v>0.3</v>
+      </c>
+      <c r="AM15">
+        <v>0.4</v>
+      </c>
+      <c r="AN15">
+        <v>0.1</v>
+      </c>
+      <c r="AO15">
+        <v>0.2</v>
+      </c>
+      <c r="AP15">
+        <v>0.3</v>
+      </c>
+      <c r="AQ15">
+        <v>0.4</v>
+      </c>
+      <c r="AR15">
+        <v>0.8</v>
+      </c>
+      <c r="AS15">
+        <v>0.6</v>
+      </c>
+      <c r="AT15">
+        <v>0.4</v>
+      </c>
+      <c r="AU15">
+        <v>0.2</v>
+      </c>
+      <c r="AV15">
+        <v>0.33250000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:48" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>0.9</v>
+      </c>
+      <c r="B16">
+        <v>0.1</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>1.4032696857709346</v>
+      </c>
+      <c r="F16">
+        <v>1.391679723207335</v>
+      </c>
+      <c r="G16">
+        <v>1.3481419848321696</v>
+      </c>
+      <c r="H16">
+        <v>1.4564030781352593</v>
+      </c>
+      <c r="I16">
+        <v>1.4032696857709346</v>
+      </c>
+      <c r="J16">
+        <v>1.4046737662074389</v>
+      </c>
+      <c r="K16">
+        <v>1.4124908022541613</v>
+      </c>
+      <c r="L16">
+        <v>1.4009153455789169</v>
+      </c>
+      <c r="M16">
+        <v>1.3950029563855542</v>
+      </c>
+      <c r="N16">
+        <v>1.3923491240665318</v>
+      </c>
+      <c r="O16">
+        <v>1.3846117281333863</v>
+      </c>
+      <c r="P16">
+        <v>1.379493368937619</v>
+      </c>
+      <c r="Q16">
+        <v>1.3627117497303625</v>
+      </c>
+      <c r="R16">
+        <v>1.3983009625161797</v>
+      </c>
+      <c r="S16">
+        <v>1.4076100662251656</v>
+      </c>
+      <c r="T16">
+        <v>1.4207370176786045</v>
+      </c>
+      <c r="U16">
+        <v>1.4264920001671997</v>
+      </c>
+      <c r="V16">
+        <v>1.4345300287236296</v>
+      </c>
+      <c r="W16">
+        <v>1.4325404002943647</v>
+      </c>
+      <c r="X16">
+        <v>1.4424274809160305</v>
+      </c>
+      <c r="Y16">
+        <v>1.4418083078192858</v>
+      </c>
+      <c r="Z16">
+        <v>1.4462850855399139</v>
+      </c>
+      <c r="AA16">
+        <v>1.3651813834175428</v>
+      </c>
+      <c r="AB16">
+        <v>1.3761291570419816</v>
+      </c>
+      <c r="AC16">
+        <v>1.3892712546345327</v>
+      </c>
+      <c r="AD16">
+        <v>1.3948582082375525</v>
+      </c>
+      <c r="AE16">
+        <v>1.4031986371622374</v>
+      </c>
+      <c r="AF16">
+        <v>1.4111064039108212</v>
+      </c>
+      <c r="AG16">
+        <v>1.4278544725082263</v>
+      </c>
+      <c r="AH16">
+        <v>1.4269853946866891</v>
+      </c>
+      <c r="AI16">
+        <v>1.4363596551875635</v>
+      </c>
+      <c r="AJ16">
+        <v>1.4099610724063587</v>
+      </c>
+      <c r="AK16">
+        <v>1.4049327305603436</v>
+      </c>
+      <c r="AL16">
+        <v>1.4174655214915524</v>
+      </c>
+      <c r="AM16">
+        <v>1.4170045491281291</v>
+      </c>
+      <c r="AN16">
+        <v>1.3759171605343226</v>
+      </c>
+      <c r="AO16">
+        <v>1.3978293410990226</v>
+      </c>
+      <c r="AP16">
+        <v>1.4075644731880785</v>
+      </c>
+      <c r="AQ16">
+        <v>1.4167807503784016</v>
+      </c>
+      <c r="AR16">
+        <v>1.4377480646198291</v>
+      </c>
+      <c r="AS16">
+        <v>1.429554630164829</v>
+      </c>
+      <c r="AT16">
+        <v>1.4130958201583113</v>
+      </c>
+      <c r="AU16">
+        <v>1.4086758669034281</v>
+      </c>
+      <c r="AV16">
+        <v>1.4167885561692719</v>
+      </c>
+    </row>
+    <row r="17" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>0.8</v>
+      </c>
+      <c r="B17">
+        <v>0.2</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>1.4046737662074389</v>
+      </c>
+    </row>
+    <row r="18" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>0.7</v>
+      </c>
+      <c r="B18">
+        <v>0.3</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>1.4124908022541613</v>
+      </c>
+      <c r="F18">
+        <f>COUNT(F16:AV16)</f>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>0.6</v>
+      </c>
+      <c r="B19">
+        <v>0.4</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>1.4009153455789169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>0.5</v>
+      </c>
+      <c r="B20">
+        <v>0.5</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>1.3950029563855542</v>
+      </c>
+    </row>
+    <row r="21" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>0.4</v>
+      </c>
+      <c r="B21">
+        <v>0.6</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>1.3923491240665318</v>
+      </c>
+    </row>
+    <row r="22" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>0.3</v>
+      </c>
+      <c r="B22">
+        <v>0.7</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>1.3846117281333863</v>
+      </c>
+      <c r="F22" t="s">
+        <v>0</v>
+      </c>
+      <c r="G22" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>10</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0.9</v>
+      </c>
+      <c r="L22">
+        <v>0.8</v>
+      </c>
+      <c r="M22">
+        <v>0.7</v>
+      </c>
+      <c r="N22">
+        <v>0.6</v>
+      </c>
+      <c r="O22">
+        <v>0.5</v>
+      </c>
+      <c r="P22">
+        <v>0.4</v>
+      </c>
+      <c r="Q22">
+        <v>0.3</v>
+      </c>
+      <c r="R22">
+        <v>0.2</v>
+      </c>
+      <c r="S22">
+        <v>0.1</v>
+      </c>
+      <c r="T22">
+        <v>0.9</v>
+      </c>
+      <c r="U22">
+        <v>0.8</v>
+      </c>
+      <c r="V22">
+        <v>0.7</v>
+      </c>
+      <c r="W22">
+        <v>0.6</v>
+      </c>
+      <c r="X22">
+        <v>0.5</v>
+      </c>
+      <c r="Y22">
+        <v>0.4</v>
+      </c>
+      <c r="Z22">
+        <v>0.3</v>
+      </c>
+      <c r="AA22">
+        <v>0.2</v>
+      </c>
+      <c r="AB22">
+        <v>0.1</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0.8</v>
+      </c>
+      <c r="AM22">
+        <v>0.6</v>
+      </c>
+      <c r="AN22">
+        <v>0.4</v>
+      </c>
+      <c r="AO22">
+        <v>0.2</v>
+      </c>
+      <c r="AP22">
+        <v>0.1</v>
+      </c>
+      <c r="AQ22">
+        <v>0.2</v>
+      </c>
+      <c r="AR22">
+        <v>0.3</v>
+      </c>
+      <c r="AS22">
+        <v>0.4</v>
+      </c>
+      <c r="AT22">
+        <v>0.1</v>
+      </c>
+      <c r="AU22">
+        <v>0.2</v>
+      </c>
+      <c r="AV22">
+        <v>0.3</v>
+      </c>
+      <c r="AW22">
+        <v>0.4</v>
+      </c>
+      <c r="AX22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>0.2</v>
+      </c>
+      <c r="B23">
+        <v>0.8</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>1.379493368937619</v>
+      </c>
+      <c r="F23" t="s">
+        <v>4</v>
+      </c>
+      <c r="G23" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0.1</v>
+      </c>
+      <c r="L23">
+        <v>0.2</v>
+      </c>
+      <c r="M23">
+        <v>0.3</v>
+      </c>
+      <c r="N23">
+        <v>0.4</v>
+      </c>
+      <c r="O23">
+        <v>0.5</v>
+      </c>
+      <c r="P23">
+        <v>0.6</v>
+      </c>
+      <c r="Q23">
+        <v>0.7</v>
+      </c>
+      <c r="R23">
+        <v>0.8</v>
+      </c>
+      <c r="S23">
+        <v>0.9</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0.9</v>
+      </c>
+      <c r="AD23">
+        <v>0.8</v>
+      </c>
+      <c r="AE23">
+        <v>0.7</v>
+      </c>
+      <c r="AF23">
+        <v>0.6</v>
+      </c>
+      <c r="AG23">
+        <v>0.5</v>
+      </c>
+      <c r="AH23">
+        <v>0.4</v>
+      </c>
+      <c r="AI23">
+        <v>0.3</v>
+      </c>
+      <c r="AJ23">
+        <v>0.2</v>
+      </c>
+      <c r="AK23">
+        <v>0.1</v>
+      </c>
+      <c r="AL23">
+        <v>0.1</v>
+      </c>
+      <c r="AM23">
+        <v>0.2</v>
+      </c>
+      <c r="AN23">
+        <v>0.3</v>
+      </c>
+      <c r="AO23">
+        <v>0.4</v>
+      </c>
+      <c r="AP23">
+        <v>0.8</v>
+      </c>
+      <c r="AQ23">
+        <v>0.6</v>
+      </c>
+      <c r="AR23">
+        <v>0.4</v>
+      </c>
+      <c r="AS23">
+        <v>0.2</v>
+      </c>
+      <c r="AT23">
+        <v>0.1</v>
+      </c>
+      <c r="AU23">
+        <v>0.2</v>
+      </c>
+      <c r="AV23">
+        <v>0.3</v>
+      </c>
+      <c r="AW23">
+        <v>0.4</v>
+      </c>
+      <c r="AX23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>0.1</v>
+      </c>
+      <c r="B24">
+        <v>0.9</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>1.3627117497303625</v>
+      </c>
+      <c r="F24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>12</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0.1</v>
+      </c>
+      <c r="U24">
+        <v>0.2</v>
+      </c>
+      <c r="V24">
+        <v>0.3</v>
+      </c>
+      <c r="W24">
+        <v>0.4</v>
+      </c>
+      <c r="X24">
+        <v>0.5</v>
+      </c>
+      <c r="Y24">
+        <v>0.6</v>
+      </c>
+      <c r="Z24">
+        <v>0.7</v>
+      </c>
+      <c r="AA24">
+        <v>0.8</v>
+      </c>
+      <c r="AB24">
+        <v>0.9</v>
+      </c>
+      <c r="AC24">
+        <v>0.1</v>
+      </c>
+      <c r="AD24">
+        <v>0.2</v>
+      </c>
+      <c r="AE24">
+        <v>0.3</v>
+      </c>
+      <c r="AF24">
+        <v>0.4</v>
+      </c>
+      <c r="AG24">
+        <v>0.5</v>
+      </c>
+      <c r="AH24">
+        <v>0.6</v>
+      </c>
+      <c r="AI24">
+        <v>0.7</v>
+      </c>
+      <c r="AJ24">
+        <v>0.8</v>
+      </c>
+      <c r="AK24">
+        <v>0.9</v>
+      </c>
+      <c r="AL24">
+        <v>0.1</v>
+      </c>
+      <c r="AM24">
+        <v>0.2</v>
+      </c>
+      <c r="AN24">
+        <v>0.3</v>
+      </c>
+      <c r="AO24">
+        <v>0.4</v>
+      </c>
+      <c r="AP24">
+        <v>0.1</v>
+      </c>
+      <c r="AQ24">
+        <v>0.2</v>
+      </c>
+      <c r="AR24">
+        <v>0.3</v>
+      </c>
+      <c r="AS24">
+        <v>0.4</v>
+      </c>
+      <c r="AT24">
+        <v>0.8</v>
+      </c>
+      <c r="AU24">
+        <v>0.6</v>
+      </c>
+      <c r="AV24">
+        <v>0.4</v>
+      </c>
+      <c r="AW24">
+        <v>0.2</v>
+      </c>
+      <c r="AX24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>0.9</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0.1</v>
+      </c>
+      <c r="D25">
+        <v>1.3983009625161797</v>
+      </c>
+    </row>
+    <row r="26" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>0.8</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0.2</v>
+      </c>
+      <c r="D26">
+        <v>1.4076100662251656</v>
+      </c>
+      <c r="I26">
+        <f>SUM(I22:I24)</f>
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <f t="shared" ref="J26:AX26" si="1">SUM(J22:J24)</f>
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="U26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="V26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="W26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="X26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Z26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AA26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AB26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AC26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AD26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AE26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AF26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AG26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AH26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AI26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AJ26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AK26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AL26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AM26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AN26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AO26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AP26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AQ26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AR26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AS26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AT26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AU26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AV26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AW26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AX26">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>0.7</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>0.3</v>
+      </c>
+      <c r="D27">
+        <v>1.4207370176786045</v>
+      </c>
+    </row>
+    <row r="28" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>0.6</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0.4</v>
+      </c>
+      <c r="D28">
+        <v>1.4264920001671997</v>
+      </c>
+      <c r="I28">
+        <f>SUM(I26:AX26)</f>
+        <v>41</v>
+      </c>
+      <c r="AX28">
+        <f>0.33375+0.33375+0.3325</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>0.5</v>
+      </c>
+      <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
+        <v>0.5</v>
+      </c>
+      <c r="D29">
+        <v>1.4345300287236296</v>
+      </c>
+    </row>
+    <row r="30" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>0.4</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>0.6</v>
+      </c>
+      <c r="D30">
+        <v>1.4325404002943647</v>
+      </c>
+    </row>
+    <row r="31" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>0.3</v>
+      </c>
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <v>0.7</v>
+      </c>
+      <c r="D31">
+        <v>1.4424274809160305</v>
+      </c>
+    </row>
+    <row r="32" spans="1:50" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>0.2</v>
+      </c>
+      <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
+        <v>0.8</v>
+      </c>
+      <c r="D32">
+        <v>1.4418083078192858</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>0.1</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33">
+        <v>0.9</v>
+      </c>
+      <c r="D33">
+        <v>1.4462850855399139</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34">
+        <v>0.9</v>
+      </c>
+      <c r="C34">
+        <v>0.1</v>
+      </c>
+      <c r="D34">
+        <v>1.3651813834175428</v>
+      </c>
+      <c r="F34">
+        <f>MAX(D13:D55)</f>
+        <v>1.4564030781352593</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35">
+        <v>0.8</v>
+      </c>
+      <c r="C35">
+        <v>0.2</v>
+      </c>
+      <c r="D35">
+        <v>1.3761291570419816</v>
+      </c>
+      <c r="F35">
+        <f>MIN(D13:D55)</f>
+        <v>1.3481419848321696</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36">
+        <v>0.7</v>
+      </c>
+      <c r="C36">
+        <v>0.3</v>
+      </c>
+      <c r="D36">
+        <v>1.3892712546345327</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37">
+        <v>0.6</v>
+      </c>
+      <c r="C37">
+        <v>0.4</v>
+      </c>
+      <c r="D37">
+        <v>1.3948582082375525</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38">
+        <v>0.5</v>
+      </c>
+      <c r="C38">
+        <v>0.5</v>
+      </c>
+      <c r="D38">
+        <v>1.4031986371622374</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39">
+        <v>0.4</v>
+      </c>
+      <c r="C39">
+        <v>0.6</v>
+      </c>
+      <c r="D39">
+        <v>1.4111064039108212</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40">
+        <v>0.3</v>
+      </c>
+      <c r="C40">
+        <v>0.7</v>
+      </c>
+      <c r="D40">
+        <v>1.4278544725082263</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41">
+        <v>0.2</v>
+      </c>
+      <c r="C41">
+        <v>0.8</v>
+      </c>
+      <c r="D41">
+        <v>1.4269853946866891</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42">
+        <v>0.1</v>
+      </c>
+      <c r="C42">
+        <v>0.9</v>
+      </c>
+      <c r="D42">
+        <v>1.4363596551875635</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>0.8</v>
+      </c>
+      <c r="B43">
+        <v>0.1</v>
+      </c>
+      <c r="C43">
+        <v>0.1</v>
+      </c>
+      <c r="D43">
+        <v>1.4099610724063587</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>0.6</v>
+      </c>
+      <c r="B44">
+        <v>0.2</v>
+      </c>
+      <c r="C44">
+        <v>0.2</v>
+      </c>
+      <c r="D44">
+        <v>1.4049327305603436</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>0.4</v>
+      </c>
+      <c r="B45">
+        <v>0.3</v>
+      </c>
+      <c r="C45">
+        <v>0.3</v>
+      </c>
+      <c r="D45">
+        <v>1.4174655214915524</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>0.2</v>
+      </c>
+      <c r="B46">
+        <v>0.4</v>
+      </c>
+      <c r="C46">
+        <v>0.4</v>
+      </c>
+      <c r="D46">
+        <v>1.4170045491281291</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>0.1</v>
+      </c>
+      <c r="B47">
+        <v>0.8</v>
+      </c>
+      <c r="C47">
+        <v>0.1</v>
+      </c>
+      <c r="D47">
+        <v>1.3759171605343226</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>0.2</v>
+      </c>
+      <c r="B48">
+        <v>0.6</v>
+      </c>
+      <c r="C48">
+        <v>0.2</v>
+      </c>
+      <c r="D48">
+        <v>1.3978293410990226</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>0.3</v>
+      </c>
+      <c r="B49">
+        <v>0.4</v>
+      </c>
+      <c r="C49">
+        <v>0.3</v>
+      </c>
+      <c r="D49">
+        <v>1.4075644731880785</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>0.4</v>
+      </c>
+      <c r="B50">
+        <v>0.2</v>
+      </c>
+      <c r="C50">
+        <v>0.4</v>
+      </c>
+      <c r="D50">
+        <v>1.4167807503784016</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>0.1</v>
+      </c>
+      <c r="B51">
+        <v>0.1</v>
+      </c>
+      <c r="C51">
+        <v>0.8</v>
+      </c>
+      <c r="D51">
+        <v>1.4377480646198291</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>0.2</v>
+      </c>
+      <c r="B52">
+        <v>0.2</v>
+      </c>
+      <c r="C52">
+        <v>0.6</v>
+      </c>
+      <c r="D52">
+        <v>1.429554630164829</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>0.3</v>
+      </c>
+      <c r="B53">
+        <v>0.3</v>
+      </c>
+      <c r="C53">
+        <v>0.4</v>
+      </c>
+      <c r="D53">
+        <v>1.4130958201583113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>0.4</v>
+      </c>
+      <c r="B54">
+        <v>0.4</v>
+      </c>
+      <c r="C54">
+        <v>0.2</v>
+      </c>
+      <c r="D54">
+        <v>1.4086758669034281</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>0.33374999999999999</v>
+      </c>
+      <c r="B55">
+        <v>0.33374999999999999</v>
+      </c>
+      <c r="C55">
+        <v>0.33250000000000002</v>
+      </c>
+      <c r="D55">
+        <v>1.4167885561692719</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3246CD1C-380B-E146-B880-21532CFA1EFF}">
+  <dimension ref="A5:AY50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="5" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>55.224105355678162</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>0.9</v>
+      </c>
+      <c r="H5">
+        <v>0.8</v>
+      </c>
+      <c r="I5">
+        <v>0.7</v>
+      </c>
+      <c r="J5">
+        <v>0.6</v>
+      </c>
+      <c r="K5">
+        <v>0.5</v>
+      </c>
+      <c r="L5">
+        <v>0.4</v>
+      </c>
+      <c r="M5">
+        <v>0.3</v>
+      </c>
+      <c r="N5">
+        <v>0.2</v>
+      </c>
+      <c r="O5">
+        <v>0.1</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>0.9</v>
+      </c>
+      <c r="S5">
+        <v>0.8</v>
+      </c>
+      <c r="T5">
+        <v>0.7</v>
+      </c>
+      <c r="U5">
+        <v>0.6</v>
+      </c>
+      <c r="V5">
+        <v>0.5</v>
+      </c>
+      <c r="W5">
+        <v>0.4</v>
+      </c>
+      <c r="X5">
+        <v>0.3</v>
+      </c>
+      <c r="Y5">
+        <v>0.2</v>
+      </c>
+      <c r="Z5">
+        <v>0.1</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0.8</v>
+      </c>
+      <c r="AN5">
+        <v>0.6</v>
+      </c>
+      <c r="AO5">
+        <v>0.4</v>
+      </c>
+      <c r="AP5">
+        <v>0.2</v>
+      </c>
+      <c r="AQ5">
+        <v>0.1</v>
+      </c>
+      <c r="AR5">
+        <v>0.2</v>
+      </c>
+      <c r="AS5">
+        <v>0.3</v>
+      </c>
+      <c r="AT5">
+        <v>0.4</v>
+      </c>
+      <c r="AU5">
+        <v>0.1</v>
+      </c>
+      <c r="AV5">
+        <v>0.2</v>
+      </c>
+      <c r="AW5">
+        <v>0.3</v>
+      </c>
+      <c r="AX5">
+        <v>0.4</v>
+      </c>
+      <c r="AY5">
+        <v>0.33374999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>0.9</v>
+      </c>
+      <c r="B6">
+        <v>0.1</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>57.458199917239284</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0.1</v>
+      </c>
+      <c r="H6">
+        <v>0.2</v>
+      </c>
+      <c r="I6">
+        <v>0.3</v>
+      </c>
+      <c r="J6">
+        <v>0.4</v>
+      </c>
+      <c r="K6">
+        <v>0.5</v>
+      </c>
+      <c r="L6">
+        <v>0.6</v>
+      </c>
+      <c r="M6">
+        <v>0.7</v>
+      </c>
+      <c r="N6">
+        <v>0.8</v>
+      </c>
+      <c r="O6">
+        <v>0.9</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>0.9</v>
+      </c>
+      <c r="AD6">
+        <v>0.8</v>
+      </c>
+      <c r="AE6">
+        <v>0.7</v>
+      </c>
+      <c r="AF6">
+        <v>0.6</v>
+      </c>
+      <c r="AG6">
+        <v>0.5</v>
+      </c>
+      <c r="AH6">
+        <v>0.4</v>
+      </c>
+      <c r="AI6">
+        <v>0.3</v>
+      </c>
+      <c r="AJ6">
+        <v>0.2</v>
+      </c>
+      <c r="AK6">
+        <v>0.1</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0.1</v>
+      </c>
+      <c r="AN6">
+        <v>0.2</v>
+      </c>
+      <c r="AO6">
+        <v>0.3</v>
+      </c>
+      <c r="AP6">
+        <v>0.4</v>
+      </c>
+      <c r="AQ6">
+        <v>0.8</v>
+      </c>
+      <c r="AR6">
+        <v>0.6</v>
+      </c>
+      <c r="AS6">
+        <v>0.4</v>
+      </c>
+      <c r="AT6">
+        <v>0.2</v>
+      </c>
+      <c r="AU6">
+        <v>0.1</v>
+      </c>
+      <c r="AV6">
+        <v>0.2</v>
+      </c>
+      <c r="AW6">
+        <v>0.3</v>
+      </c>
+      <c r="AX6">
+        <v>0.4</v>
+      </c>
+      <c r="AY6">
+        <v>0.33374999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>0.8</v>
+      </c>
+      <c r="B7">
+        <v>0.2</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>56.473661589464839</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0.1</v>
+      </c>
+      <c r="S7">
+        <v>0.2</v>
+      </c>
+      <c r="T7">
+        <v>0.3</v>
+      </c>
+      <c r="U7">
+        <v>0.4</v>
+      </c>
+      <c r="V7">
+        <v>0.5</v>
+      </c>
+      <c r="W7">
+        <v>0.6</v>
+      </c>
+      <c r="X7">
+        <v>0.7</v>
+      </c>
+      <c r="Y7">
+        <v>0.8</v>
+      </c>
+      <c r="Z7">
+        <v>0.9</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0.1</v>
+      </c>
+      <c r="AD7">
+        <v>0.2</v>
+      </c>
+      <c r="AE7">
+        <v>0.3</v>
+      </c>
+      <c r="AF7">
+        <v>0.4</v>
+      </c>
+      <c r="AG7">
+        <v>0.5</v>
+      </c>
+      <c r="AH7">
+        <v>0.6</v>
+      </c>
+      <c r="AI7">
+        <v>0.7</v>
+      </c>
+      <c r="AJ7">
+        <v>0.8</v>
+      </c>
+      <c r="AK7">
+        <v>0.9</v>
+      </c>
+      <c r="AL7">
+        <v>1</v>
+      </c>
+      <c r="AM7">
+        <v>0.1</v>
+      </c>
+      <c r="AN7">
+        <v>0.2</v>
+      </c>
+      <c r="AO7">
+        <v>0.3</v>
+      </c>
+      <c r="AP7">
+        <v>0.4</v>
+      </c>
+      <c r="AQ7">
+        <v>0.1</v>
+      </c>
+      <c r="AR7">
+        <v>0.2</v>
+      </c>
+      <c r="AS7">
+        <v>0.3</v>
+      </c>
+      <c r="AT7">
+        <v>0.4</v>
+      </c>
+      <c r="AU7">
+        <v>0.8</v>
+      </c>
+      <c r="AV7">
+        <v>0.6</v>
+      </c>
+      <c r="AW7">
+        <v>0.4</v>
+      </c>
+      <c r="AX7">
+        <v>0.2</v>
+      </c>
+      <c r="AY7">
+        <v>0.33250000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>0.7</v>
+      </c>
+      <c r="B8">
+        <v>0.3</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>57.948506654830574</v>
+      </c>
+      <c r="F8">
+        <v>55.224105355678162</v>
+      </c>
+      <c r="G8">
+        <v>57.458199917239284</v>
+      </c>
+      <c r="H8">
+        <v>56.473661589464839</v>
+      </c>
+      <c r="I8">
+        <v>57.948506654830574</v>
+      </c>
+      <c r="J8">
+        <v>58.47758045011485</v>
+      </c>
+      <c r="K8">
+        <v>62.271604643317296</v>
+      </c>
+      <c r="L8">
+        <v>60.872390755163273</v>
+      </c>
+      <c r="M8">
+        <v>60.447060675606345</v>
+      </c>
+      <c r="N8">
+        <v>59.996789572920363</v>
+      </c>
+      <c r="O8">
+        <v>60.606817595591224</v>
+      </c>
+      <c r="P8">
+        <v>64.045258244474425</v>
+      </c>
+      <c r="Q8">
+        <v>55.224105355678162</v>
+      </c>
+      <c r="R8">
+        <v>55.5405035635304</v>
+      </c>
+      <c r="S8">
+        <v>56.407589133141869</v>
+      </c>
+      <c r="T8">
+        <v>57.950763569681108</v>
+      </c>
+      <c r="U8">
+        <v>57.084666337707134</v>
+      </c>
+      <c r="V8">
+        <v>56.750447715011973</v>
+      </c>
+      <c r="W8">
+        <v>59.431755662763003</v>
+      </c>
+      <c r="X8">
+        <v>58.740559507580137</v>
+      </c>
+      <c r="Y8">
+        <v>59.328127874751381</v>
+      </c>
+      <c r="Z8">
+        <v>59.871186790868684</v>
+      </c>
+      <c r="AA8">
+        <v>56.257763925440777</v>
+      </c>
+      <c r="AB8">
+        <v>64.045258244474425</v>
+      </c>
+      <c r="AC8">
+        <v>61.214970113634635</v>
+      </c>
+      <c r="AD8">
+        <v>60.937867896137739</v>
+      </c>
+      <c r="AE8">
+        <v>60.255564554395271</v>
+      </c>
+      <c r="AF8">
+        <v>60.532153660710001</v>
+      </c>
+      <c r="AG8">
+        <v>62.132270659110191</v>
+      </c>
+      <c r="AH8">
+        <v>62.792670663325708</v>
+      </c>
+      <c r="AI8">
+        <v>61.528373842675471</v>
+      </c>
+      <c r="AJ8">
+        <v>59.470753463237777</v>
+      </c>
+      <c r="AK8">
+        <v>60.632507746511223</v>
+      </c>
+      <c r="AL8">
+        <v>56.257763925440777</v>
+      </c>
+      <c r="AM8">
+        <v>56.99899172991001</v>
+      </c>
+      <c r="AN8">
+        <v>60.95570727746221</v>
+      </c>
+      <c r="AO8">
+        <v>58.536499639014863</v>
+      </c>
+      <c r="AP8">
+        <v>58.645490538989975</v>
+      </c>
+      <c r="AQ8">
+        <v>59.909399611177719</v>
+      </c>
+      <c r="AR8">
+        <v>60.643958857920403</v>
+      </c>
+      <c r="AS8">
+        <v>57.911541364663684</v>
+      </c>
+      <c r="AT8">
+        <v>60.27621615236616</v>
+      </c>
+      <c r="AU8">
+        <v>58.789225618420147</v>
+      </c>
+      <c r="AV8">
+        <v>61.004416595092053</v>
+      </c>
+      <c r="AW8">
+        <v>61.128157565171882</v>
+      </c>
+      <c r="AX8">
+        <v>59.066140299925145</v>
+      </c>
+      <c r="AY8">
+        <v>59.762637393799501</v>
+      </c>
+    </row>
+    <row r="9" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>0.6</v>
+      </c>
+      <c r="B9">
+        <v>0.4</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>58.47758045011485</v>
+      </c>
+    </row>
+    <row r="10" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>0.5</v>
+      </c>
+      <c r="B10">
+        <v>0.5</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>62.271604643317296</v>
+      </c>
+    </row>
+    <row r="11" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>0.4</v>
+      </c>
+      <c r="B11">
+        <v>0.6</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>60.872390755163273</v>
+      </c>
+    </row>
+    <row r="12" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>0.3</v>
+      </c>
+      <c r="B12">
+        <v>0.7</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>60.447060675606345</v>
+      </c>
+    </row>
+    <row r="13" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>0.2</v>
+      </c>
+      <c r="B13">
+        <v>0.8</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>59.996789572920363</v>
+      </c>
+    </row>
+    <row r="14" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>0.1</v>
+      </c>
+      <c r="B14">
+        <v>0.9</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>60.606817595591224</v>
+      </c>
+    </row>
+    <row r="15" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>64.045258244474425</v>
+      </c>
+    </row>
+    <row r="16" spans="1:51" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>55.224105355678162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>0.9</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0.1</v>
+      </c>
+      <c r="D17">
+        <v>55.5405035635304</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>0.8</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0.2</v>
+      </c>
+      <c r="D18">
+        <v>56.407589133141869</v>
+      </c>
+      <c r="F18">
+        <f>MAX(D5:D50)</f>
+        <v>64.045258244474425</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>0.7</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0.3</v>
+      </c>
+      <c r="D19">
+        <v>57.950763569681108</v>
+      </c>
+      <c r="F19">
+        <f>MIN(D5:D50)</f>
+        <v>55.224105355678162</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>0.6</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0.4</v>
+      </c>
+      <c r="D20">
+        <v>57.084666337707134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>0.5</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0.5</v>
+      </c>
+      <c r="D21">
+        <v>56.750447715011973</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>0.4</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0.6</v>
+      </c>
+      <c r="D22">
+        <v>59.431755662763003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>0.3</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0.7</v>
+      </c>
+      <c r="D23">
+        <v>58.740559507580137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>0.2</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0.8</v>
+      </c>
+      <c r="D24">
+        <v>59.328127874751381</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>0.1</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0.9</v>
+      </c>
+      <c r="D25">
+        <v>59.871186790868684</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>56.257763925440777</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>64.045258244474425</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28">
+        <v>0.9</v>
+      </c>
+      <c r="C28">
+        <v>0.1</v>
+      </c>
+      <c r="D28">
+        <v>61.214970113634635</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29">
+        <v>0.8</v>
+      </c>
+      <c r="C29">
+        <v>0.2</v>
+      </c>
+      <c r="D29">
+        <v>60.937867896137739</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>0.7</v>
+      </c>
+      <c r="C30">
+        <v>0.3</v>
+      </c>
+      <c r="D30">
+        <v>60.255564554395271</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31">
+        <v>0.6</v>
+      </c>
+      <c r="C31">
+        <v>0.4</v>
+      </c>
+      <c r="D31">
+        <v>60.532153660710001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32">
+        <v>0.5</v>
+      </c>
+      <c r="C32">
+        <v>0.5</v>
+      </c>
+      <c r="D32">
+        <v>62.132270659110191</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33">
+        <v>0.4</v>
+      </c>
+      <c r="C33">
+        <v>0.6</v>
+      </c>
+      <c r="D33">
+        <v>62.792670663325708</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34">
+        <v>0.3</v>
+      </c>
+      <c r="C34">
+        <v>0.7</v>
+      </c>
+      <c r="D34">
+        <v>61.528373842675471</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35">
+        <v>0.2</v>
+      </c>
+      <c r="C35">
+        <v>0.8</v>
+      </c>
+      <c r="D35">
+        <v>59.470753463237777</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36">
+        <v>0.1</v>
+      </c>
+      <c r="C36">
+        <v>0.9</v>
+      </c>
+      <c r="D36">
+        <v>60.632507746511223</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>56.257763925440777</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>0.8</v>
+      </c>
+      <c r="B38">
+        <v>0.1</v>
+      </c>
+      <c r="C38">
+        <v>0.1</v>
+      </c>
+      <c r="D38">
+        <v>56.99899172991001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>0.6</v>
+      </c>
+      <c r="B39">
+        <v>0.2</v>
+      </c>
+      <c r="C39">
+        <v>0.2</v>
+      </c>
+      <c r="D39">
+        <v>60.95570727746221</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>0.4</v>
+      </c>
+      <c r="B40">
+        <v>0.3</v>
+      </c>
+      <c r="C40">
+        <v>0.3</v>
+      </c>
+      <c r="D40">
+        <v>58.536499639014863</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>0.2</v>
+      </c>
+      <c r="B41">
+        <v>0.4</v>
+      </c>
+      <c r="C41">
+        <v>0.4</v>
+      </c>
+      <c r="D41">
+        <v>58.645490538989975</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>0.1</v>
+      </c>
+      <c r="B42">
+        <v>0.8</v>
+      </c>
+      <c r="C42">
+        <v>0.1</v>
+      </c>
+      <c r="D42">
+        <v>59.909399611177719</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>0.2</v>
+      </c>
+      <c r="B43">
+        <v>0.6</v>
+      </c>
+      <c r="C43">
+        <v>0.2</v>
+      </c>
+      <c r="D43">
+        <v>60.643958857920403</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>0.3</v>
+      </c>
+      <c r="B44">
+        <v>0.4</v>
+      </c>
+      <c r="C44">
+        <v>0.3</v>
+      </c>
+      <c r="D44">
+        <v>57.911541364663684</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>0.4</v>
+      </c>
+      <c r="B45">
+        <v>0.2</v>
+      </c>
+      <c r="C45">
+        <v>0.4</v>
+      </c>
+      <c r="D45">
+        <v>60.27621615236616</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>0.1</v>
+      </c>
+      <c r="B46">
+        <v>0.1</v>
+      </c>
+      <c r="C46">
+        <v>0.8</v>
+      </c>
+      <c r="D46">
+        <v>58.789225618420147</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>0.2</v>
+      </c>
+      <c r="B47">
+        <v>0.2</v>
+      </c>
+      <c r="C47">
+        <v>0.6</v>
+      </c>
+      <c r="D47">
+        <v>61.004416595092053</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>0.3</v>
+      </c>
+      <c r="B48">
+        <v>0.3</v>
+      </c>
+      <c r="C48">
+        <v>0.4</v>
+      </c>
+      <c r="D48">
+        <v>61.128157565171882</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>0.4</v>
+      </c>
+      <c r="B49">
+        <v>0.4</v>
+      </c>
+      <c r="C49">
+        <v>0.2</v>
+      </c>
+      <c r="D49">
+        <v>59.066140299925145</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>0.33374999999999999</v>
+      </c>
+      <c r="B50">
+        <v>0.33374999999999999</v>
+      </c>
+      <c r="C50">
+        <v>0.33250000000000002</v>
+      </c>
+      <c r="D50">
+        <v>59.762637393799501</v>
       </c>
     </row>
   </sheetData>
